--- a/public/templates/forms/A-160-VulnerabilityScanningSchedule-FORM.xlsx
+++ b/public/templates/forms/A-160-VulnerabilityScanningSchedule-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Schedule!$10:$10</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -261,6 +266,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -661,7 +672,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>[Automated vulnerability scan]</t>
@@ -698,7 +709,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
           <t>[Authenticated / credentialed scan]</t>
@@ -735,7 +746,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>[Penetration test (independent assessor)]</t>
@@ -772,7 +783,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>[Independent control assessment]</t>
@@ -879,7 +890,6 @@
       <c r="B23" s="25" t="n"/>
       <c r="C23" s="13">
         <f>COUNTA(A11:A20)</f>
-        <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -891,7 +901,6 @@
       <c r="B24" s="25" t="n"/>
       <c r="C24" s="13">
         <f>COUNTIF(G11:G20,"&lt;"&amp;TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -913,7 +922,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="48" customHeight="1">
+    <row r="29" ht="50.5" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>When a scan or assessment is past due, the [Owner role] is notified and the item is completed or rescheduled within [10 business days]. Findings from every scan and assessment are recorded in the Vulnerability Assessment Reports and tracked to closure in the Risk / Finding Register (POA&amp;M).</t>
@@ -1064,7 +1073,7 @@
       <c r="E46" s="12" t="n"/>
       <c r="F46" s="12" t="n"/>
     </row>
-    <row r="48" ht="60" customHeight="1">
+    <row r="48" ht="66.4" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Drafter's note (internal, delete before publishing): rows are a starting cadence (routine scans plus an annual penetration test and independent assessment); confirm frequencies against the agency's risk posture. Penetration tests and independent assessments produce Vulnerability Assessment Reports. Agency-supplied values left in brackets: [Agency Name], owner roles, version and dates, and every frequency, last-run, and next-due value.</t>
@@ -1102,14 +1111,18 @@
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="F11:F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
       <formula1>"On track,Due soon,Overdue,Complete"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation sqref="D11:D20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Frequency" prompt="Select a value" type="list">
+      <formula1>"Monthly,Quarterly,Annually"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1135,14 +1148,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="43.5" customHeight="1">
+    <row r="2" ht="50.5" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>How to use this template: replace every [BRACKETED] field with your agency's information and follow the « » guidance notes, then delete every « » note before publishing. This sheet explains each column; it is guidance only and can be removed once the schedule is populated.</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, escalation, sign-off and revision history live on the Schedule tab.</t>
@@ -1178,7 +1191,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="17" t="inlineStr">
         <is>
           <t>Scan / assessment activity</t>
@@ -1222,7 +1235,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Tool / method</t>
@@ -1266,7 +1279,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Owner (role)</t>
@@ -1304,10 +1317,8 @@
           <t>Optional</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
+      <c r="D12" s="26">
+        <v>46082</v>
       </c>
     </row>
     <row r="13">
@@ -1326,10 +1337,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
+      <c r="D13" s="27">
+        <v>46113</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1418,6 +1427,6 @@
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>